--- a/data/processed/harmonization/Carbon__Total_carbon/10.5440_1854940/10.5440_1854940_soil_Carbon__Total_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Total_carbon/10.5440_1854940/10.5440_1854940_soil_Carbon__Total_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:183</t>
+          <t>TL_MM27:0-6.2:2019-08-22:183</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:172</t>
+          <t>TL_MM27:17-23.5:2019-08-22:172</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:185</t>
+          <t>TL_MM27:14.5-20.5:2019-08-22:185</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:167</t>
+          <t>TL_MM27:10-17:2019-08-22:167</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:184</t>
+          <t>TL_MM27:0-6.25:2019-08-22:184</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:181</t>
+          <t>TL_MM27:7-14.5:2019-08-22:181</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:175</t>
+          <t>TL_MM27:12-18:2019-08-23:175</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:176</t>
+          <t>TL_MM27:6-12:2019-08-23:176</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:182</t>
+          <t>TL_MM27:6.25-12.5:2019-08-23:182</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:171</t>
+          <t>TL_MM27:0-6.25:2019-08-23:171</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:163</t>
+          <t>TL_MM27:6.25-12:2019-08-23:163</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:170</t>
+          <t>TL_MM27:12-18:2019-08-23:170</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:174</t>
+          <t>TL_MM27:0-6.25:2019-08-23:174</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:189</t>
+          <t>TL_MM27:7-12:2019-08-23:189</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:188</t>
+          <t>KG_MM64:12.5-18.75:2019-08-24:188</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:186</t>
+          <t>KG_MM64:0-6.25:2019-08-24:186</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:190</t>
+          <t>KG_MM64:6.25-12.5:2019-08-24:190</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:187</t>
+          <t>KG_MM64:6.25-12.5:2019-08-24:187</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:178</t>
+          <t>KG_MM64:6.25-12.5:2019-08-24:178</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:180</t>
+          <t>KG_MM64:0-6.25:2019-08-24:180</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:192</t>
+          <t>KG_MM64:12.5-18.75:2019-08-24:192</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:140</t>
+          <t>KG_MM64:12.5-18.75:2019-08-24:140</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
